--- a/assets/downloads/CotizacionEdwing Saavedra Valeriano.xlsx
+++ b/assets/downloads/CotizacionEdwing Saavedra Valeriano.xlsx
@@ -167,7 +167,7 @@
     <t>PRECIO UNIT. (SOLES)</t>
   </si>
   <si>
-    <t>SPACIBA</t>
+    <t>Hello</t>
   </si>
   <si>
     <t>NOTAS:</t>
@@ -426,7 +426,7 @@
     <t>N.Proveedor</t>
   </si>
   <si>
-    <t>MIn ho</t>
+    <t>nhnh</t>
   </si>
   <si>
     <t>N° Cajas</t>

--- a/assets/downloads/CotizacionEdwing Saavedra Valeriano.xlsx
+++ b/assets/downloads/CotizacionEdwing Saavedra Valeriano.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="1" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId4"/>
@@ -113,9 +113,9 @@
     <t>Hola Edwing Saavedra Valeriano 😁 un gusto saludarte!
         A continuación te envío la cotización final de tu importación📋📦.
         🙋‍♂️ PAGO PENDIENTE :
-        ☑️Costo CBM: $4.752
+        ☑️Costo CBM: $1108.79604
         ☑️Impuestos: $3455.28
-        ☑️ Total: $3460.032
+        ☑️ Total: $4564.07604
         Pronto le aviso nuevos avances, que tengan buen día🚢
         Último día de pago:</t>
   </si>
@@ -2151,7 +2151,7 @@
       <c r="I30" s="49"/>
       <c r="J30" s="49"/>
       <c r="K30" s="14" t="str">
-        <f>'2'!AB7*J11</f>
+        <f>IF('2'!AF7&lt;1, '2'!AF7*J11, '2'!AF7*J11)</f>
         <v>0</v>
       </c>
       <c r="L30" s="9" t="s">

--- a/assets/downloads/CotizacionEdwing Saavedra Valeriano.xlsx
+++ b/assets/downloads/CotizacionEdwing Saavedra Valeriano.xlsx
@@ -1800,8 +1800,9 @@
       <c r="I11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="95">
-        <v>100</v>
+      <c r="J11" s="95" t="str">
+        <f>'2'!AB7</f>
+        <v>0</v>
       </c>
       <c r="K11" s="73"/>
       <c r="L11" s="73"/>

--- a/assets/downloads/CotizacionEdwing Saavedra Valeriano.xlsx
+++ b/assets/downloads/CotizacionEdwing Saavedra Valeriano.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="137">
   <si>
     <t>PRO MUNDO COMEX S.A.C.</t>
   </si>
@@ -53,28 +53,31 @@
     <t>PESO:</t>
   </si>
   <si>
-    <t>0 Kg</t>
+    <t>2.275 Tn</t>
   </si>
   <si>
     <t>DNI/RUC:</t>
   </si>
   <si>
+    <t>ORIGEN:</t>
+  </si>
+  <si>
+    <t>CHINA</t>
+  </si>
+  <si>
+    <t>MEDIDA:</t>
+  </si>
+  <si>
+    <t>TELEFONO:</t>
+  </si>
+  <si>
+    <t>915 125 848</t>
+  </si>
+  <si>
+    <t>CLIENTE:</t>
+  </si>
+  <si>
     <t>NUEVO</t>
-  </si>
-  <si>
-    <t>ORIGEN:</t>
-  </si>
-  <si>
-    <t>CHINA</t>
-  </si>
-  <si>
-    <t>MEDIDA:</t>
-  </si>
-  <si>
-    <t>TELEFONO:</t>
-  </si>
-  <si>
-    <t>CLIENTE:</t>
   </si>
   <si>
     <t>CBM</t>
@@ -113,9 +116,9 @@
     <t>Hola Edwing Saavedra Valeriano 😁 un gusto saludarte!
         A continuación te envío la cotización final de tu importación📋📦.
         🙋‍♂️ PAGO PENDIENTE :
-        ☑️Costo CBM: $1108.79604
-        ☑️Impuestos: $3455.28
-        ☑️ Total: $4564.07604
+        ☑️Costo CBM: $0
+        ☑️Impuestos: $2959.53
+        ☑️ Total: $2959.53
         Pronto le aviso nuevos avances, que tengan buen día🚢
         Último día de pago:</t>
   </si>
@@ -558,7 +561,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="11">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     <numFmt numFmtId="165" formatCode="[$$-409]#,##0"/>
     <numFmt numFmtId="166" formatCode="_-[$$-540A]* #,##0.00_ ;_-[$$-540A]* \-#,##0.00\ ;_-[$$-540A]* &quot;-&quot;??_ ;_-@_ "/>
@@ -567,9 +570,8 @@
     <numFmt numFmtId="169" formatCode="0.0\ &quot;cm&quot;"/>
     <numFmt numFmtId="170" formatCode="#,##0.000\ &quot;m3&quot;"/>
     <numFmt numFmtId="171" formatCode="&quot;$&quot;#,##0.00_-"/>
-    <numFmt numFmtId="172" formatCode="0.00&quot; Kg&quot;"/>
+    <numFmt numFmtId="172" formatCode="0.00&quot; tn&quot;"/>
     <numFmt numFmtId="173" formatCode="&quot;S/.&quot; #,##0.00_-"/>
-    <numFmt numFmtId="174" formatCode="0 &quot;m3&quot;"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -1209,7 +1211,7 @@
     <xf xfId="0" fontId="19" numFmtId="171" fillId="3" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="174" fillId="7" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="2" numFmtId="4" fillId="7" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="1" fillId="7" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
@@ -1762,20 +1764,20 @@
       <c r="B10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="16" t="s">
-        <v>13</v>
+      <c r="C10" s="16">
+        <v>25866466</v>
       </c>
       <c r="D10" s="34"/>
       <c r="E10" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="43" t="s">
         <v>14</v>
-      </c>
-      <c r="F10" s="43" t="s">
-        <v>15</v>
       </c>
       <c r="G10" s="44"/>
       <c r="H10" s="33"/>
       <c r="I10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J10" s="63"/>
       <c r="K10" s="96"/>
@@ -1783,22 +1785,22 @@
     </row>
     <row r="11" spans="1:14">
       <c r="B11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="17" t="s">
         <v>17</v>
-      </c>
-      <c r="C11" s="17">
-        <v>25866466</v>
       </c>
       <c r="D11" s="35"/>
       <c r="E11" s="24" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="48" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G11" s="65"/>
       <c r="H11" s="33"/>
       <c r="I11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J11" s="95" t="str">
         <f>'2'!AB7</f>
@@ -1822,7 +1824,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="B13" s="66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" s="66"/>
       <c r="D13" s="66"/>
@@ -1833,15 +1835,15 @@
       <c r="I13" s="66"/>
       <c r="J13" s="66"/>
       <c r="K13" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="B14" s="67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" s="67"/>
       <c r="D14" s="67"/>
@@ -1856,12 +1858,12 @@
         <v>0</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="B15" s="68" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" s="68"/>
       <c r="D15" s="68"/>
@@ -1876,12 +1878,12 @@
         <v>0</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="B16" s="51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" s="51"/>
       <c r="D16" s="51"/>
@@ -1896,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1927,7 +1929,7 @@
     </row>
     <row r="19" spans="1:14">
       <c r="B19" s="69" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19" s="69"/>
       <c r="D19" s="69"/>
@@ -1937,18 +1939,18 @@
       <c r="H19" s="18"/>
       <c r="I19" s="18"/>
       <c r="J19" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="B20" s="49" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C20" s="49"/>
       <c r="D20" s="49"/>
@@ -1966,15 +1968,15 @@
         <v>0</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="B21" s="49" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C21" s="49"/>
       <c r="D21" s="49"/>
@@ -1991,12 +1993,12 @@
         <v>0</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="B22" s="48" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C22" s="48"/>
       <c r="D22" s="48"/>
@@ -2013,12 +2015,12 @@
         <v>0</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="B23" s="51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C23" s="51"/>
       <c r="D23" s="51"/>
@@ -2033,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -2051,7 +2053,7 @@
     </row>
     <row r="25" spans="1:14">
       <c r="B25" s="48" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C25" s="48"/>
       <c r="D25" s="48"/>
@@ -2061,19 +2063,19 @@
       <c r="H25" s="48"/>
       <c r="I25" s="48"/>
       <c r="J25" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K25" s="15" t="str">
         <f>'2'!AB31</f>
         <v>0</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="B26" s="51" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C26" s="51"/>
       <c r="D26" s="51"/>
@@ -2087,7 +2089,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -2102,7 +2104,7 @@
     </row>
     <row r="28" spans="1:14" customHeight="1" ht="15.6">
       <c r="B28" s="52" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C28" s="52"/>
       <c r="D28" s="52"/>
@@ -2113,15 +2115,15 @@
       <c r="I28" s="52"/>
       <c r="J28" s="52"/>
       <c r="K28" s="28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L28" s="28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="B29" s="49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C29" s="49"/>
       <c r="D29" s="49"/>
@@ -2136,12 +2138,12 @@
         <v>0</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="B30" s="49" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C30" s="49"/>
       <c r="D30" s="49"/>
@@ -2156,12 +2158,12 @@
         <v>0</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="B31" s="48" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C31" s="48"/>
       <c r="D31" s="48"/>
@@ -2176,12 +2178,12 @@
         <v>0</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="B32" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C32" s="51"/>
       <c r="D32" s="51"/>
@@ -2196,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -2214,7 +2216,7 @@
     </row>
     <row r="34" spans="1:14">
       <c r="B34" s="59" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C34" s="60"/>
       <c r="D34" s="60"/>
@@ -2229,28 +2231,28 @@
     </row>
     <row r="35" spans="1:14">
       <c r="B35" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C35" s="56" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D35" s="57"/>
       <c r="E35" s="58"/>
       <c r="F35" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G35" s="56" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H35" s="58"/>
       <c r="I35" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J35" s="26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K35" s="47" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L35" s="47"/>
     </row>
@@ -2259,7 +2261,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
@@ -2292,7 +2294,7 @@
         <v>2</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
@@ -2325,7 +2327,7 @@
         <v>3</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
@@ -2358,7 +2360,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
@@ -2391,7 +2393,7 @@
         <v>5</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -2423,7 +2425,7 @@
         <v>6</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
@@ -2455,7 +2457,7 @@
         <v>7</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
@@ -2487,7 +2489,7 @@
         <v>8</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
@@ -2519,7 +2521,7 @@
         <v>9</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
@@ -2551,7 +2553,7 @@
         <v>10</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
@@ -2583,7 +2585,7 @@
         <v>11</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
@@ -2615,7 +2617,7 @@
         <v>12</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
@@ -2647,7 +2649,7 @@
         <v>13</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
@@ -2679,7 +2681,7 @@
         <v>14</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
@@ -2711,7 +2713,7 @@
         <v>15</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
@@ -2743,7 +2745,7 @@
         <v>16</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
@@ -2775,7 +2777,7 @@
         <v>17</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
@@ -2807,7 +2809,7 @@
         <v>18</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
@@ -2839,7 +2841,7 @@
         <v>19</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
@@ -2871,7 +2873,7 @@
         <v>20</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
@@ -2903,7 +2905,7 @@
         <v>21</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
@@ -2935,7 +2937,7 @@
         <v>22</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
@@ -2967,7 +2969,7 @@
         <v>23</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
@@ -2999,7 +3001,7 @@
         <v>24</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
@@ -3031,7 +3033,7 @@
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
@@ -3060,7 +3062,7 @@
     </row>
     <row r="61" spans="1:14" customHeight="1" ht="18">
       <c r="B61" s="93" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C61" s="92"/>
       <c r="D61" s="92"/>
@@ -3185,7 +3187,7 @@
     </row>
     <row r="64" spans="1:14" customHeight="1" ht="18">
       <c r="B64" s="64" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C64" s="64"/>
       <c r="D64" s="64"/>
@@ -3284,7 +3286,7 @@
       <c r="B69" s="38"/>
       <c r="C69" s="38"/>
       <c r="D69" s="53" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E69" s="53"/>
       <c r="F69" s="53"/>
@@ -3302,7 +3304,7 @@
     </row>
     <row r="72" spans="1:14" customHeight="1" ht="21">
       <c r="B72" s="70" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C72" s="70"/>
       <c r="D72" s="70"/>
@@ -3317,7 +3319,7 @@
     </row>
     <row r="74" spans="1:14">
       <c r="B74" s="71" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C74" s="71"/>
       <c r="D74" s="71"/>
@@ -3332,7 +3334,7 @@
     </row>
     <row r="75" spans="1:14">
       <c r="B75" s="71" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C75" s="71"/>
       <c r="D75" s="71"/>
@@ -3347,7 +3349,7 @@
     </row>
     <row r="76" spans="1:14">
       <c r="B76" s="49" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C76" s="49"/>
       <c r="D76" s="49"/>
@@ -3362,7 +3364,7 @@
     </row>
     <row r="77" spans="1:14">
       <c r="B77" s="71" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C77" s="71"/>
       <c r="D77" s="71"/>
@@ -3377,7 +3379,7 @@
     </row>
     <row r="78" spans="1:14">
       <c r="B78" s="71" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C78" s="71"/>
       <c r="D78" s="71"/>
@@ -3392,7 +3394,7 @@
     </row>
     <row r="79" spans="1:14">
       <c r="B79" s="49" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C79" s="49"/>
       <c r="D79" s="49"/>
@@ -3407,7 +3409,7 @@
     </row>
     <row r="80" spans="1:14">
       <c r="B80" s="71" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C80" s="71"/>
       <c r="D80" s="71"/>
@@ -3422,7 +3424,7 @@
     </row>
     <row r="81" spans="1:14">
       <c r="B81" s="71" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C81" s="71"/>
       <c r="D81" s="71"/>
@@ -3437,7 +3439,7 @@
     </row>
     <row r="82" spans="1:14">
       <c r="B82" s="71" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C82" s="71"/>
       <c r="D82" s="71"/>
@@ -3452,7 +3454,7 @@
     </row>
     <row r="83" spans="1:14">
       <c r="B83" s="71" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C83" s="71"/>
       <c r="D83" s="71"/>
@@ -3467,7 +3469,7 @@
     </row>
     <row r="84" spans="1:14">
       <c r="B84" s="71" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C84" s="71"/>
       <c r="D84" s="71"/>
@@ -3482,7 +3484,7 @@
     </row>
     <row r="85" spans="1:14">
       <c r="B85" s="71" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C85" s="71"/>
       <c r="D85" s="71"/>
@@ -3497,7 +3499,7 @@
     </row>
     <row r="86" spans="1:14">
       <c r="B86" s="71" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C86" s="71"/>
       <c r="D86" s="71"/>
@@ -3512,7 +3514,7 @@
     </row>
     <row r="87" spans="1:14">
       <c r="B87" s="71" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C87" s="71"/>
       <c r="D87" s="71"/>
@@ -3527,7 +3529,7 @@
     </row>
     <row r="88" spans="1:14">
       <c r="B88" s="71" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C88" s="71"/>
       <c r="D88" s="71"/>
@@ -3542,7 +3544,7 @@
     </row>
     <row r="89" spans="1:14">
       <c r="B89" s="71" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C89" s="71"/>
       <c r="D89" s="71"/>
@@ -3600,7 +3602,7 @@
     </row>
     <row r="91" spans="1:14">
       <c r="B91" s="67" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C91" s="67"/>
       <c r="D91" s="67"/>
@@ -3615,7 +3617,7 @@
     </row>
     <row r="92" spans="1:14">
       <c r="B92" s="71" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C92" s="71"/>
       <c r="D92" s="71"/>
@@ -3630,7 +3632,7 @@
     </row>
     <row r="93" spans="1:14">
       <c r="B93" s="67" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C93" s="67"/>
       <c r="D93" s="67"/>
@@ -3645,7 +3647,7 @@
     </row>
     <row r="94" spans="1:14">
       <c r="B94" s="71" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C94" s="71"/>
       <c r="D94" s="71"/>
@@ -3660,7 +3662,7 @@
     </row>
     <row r="95" spans="1:14">
       <c r="B95" s="71" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C95" s="71"/>
       <c r="D95" s="71"/>
@@ -3675,7 +3677,7 @@
     </row>
     <row r="96" spans="1:14">
       <c r="B96" s="71" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C96" s="71"/>
       <c r="D96" s="71"/>
@@ -3690,7 +3692,7 @@
     </row>
     <row r="97" spans="1:14">
       <c r="B97" s="71" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C97" s="71"/>
       <c r="D97" s="71"/>
@@ -3705,7 +3707,7 @@
     </row>
     <row r="98" spans="1:14">
       <c r="B98" s="71" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C98" s="71"/>
       <c r="D98" s="71"/>
@@ -3721,7 +3723,7 @@
     <row r="99" spans="1:14">
       <c r="A99" s="32"/>
       <c r="B99" s="72" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C99" s="72"/>
       <c r="D99" s="72"/>
@@ -3737,7 +3739,7 @@
     <row r="100" spans="1:14">
       <c r="A100" s="32"/>
       <c r="B100" s="71" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C100" s="71"/>
       <c r="D100" s="71"/>
@@ -3753,7 +3755,7 @@
     <row r="101" spans="1:14">
       <c r="A101" s="32"/>
       <c r="B101" s="72" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C101" s="72"/>
       <c r="D101" s="72"/>
@@ -4091,7 +4093,7 @@
   <sheetData>
     <row r="3" spans="1:32">
       <c r="B3" s="75" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C3" s="74"/>
       <c r="D3" s="74"/>
@@ -4101,90 +4103,90 @@
     </row>
     <row r="5" spans="1:32">
       <c r="B5" s="78" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C5" s="80" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" s="80" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" s="80" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F5" s="80" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G5" s="80" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H5" s="80" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I5" s="80" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J5" s="80" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K5" s="80" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L5" s="80" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M5" s="80" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N5" s="80" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O5" s="80" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P5" s="80" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q5" s="80" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R5" s="80" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S5" s="80" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T5" s="80" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="U5" s="80" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V5" s="80" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="W5" s="80" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="X5" s="80" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Y5" s="80" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z5" s="80" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AA5" s="80" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AB5" s="80" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:32">
       <c r="B6" s="74" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" s="74">
         <v>0</v>
@@ -4262,18 +4264,18 @@
         <v>0</v>
       </c>
       <c r="AB6" s="82">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE6" s="76" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AF6" s="76" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:32">
       <c r="B7" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C7" s="74">
         <v>0</v>
@@ -4351,18 +4353,16 @@
         <v>0</v>
       </c>
       <c r="AB7" s="83">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE7" s="77" t="s">
-        <v>13</v>
-      </c>
-      <c r="AF7" s="77">
-        <v>933.33</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="AF7" s="77"/>
     </row>
     <row r="8" spans="1:32">
       <c r="B8" s="74" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C8" s="81">
         <v>17.28</v>
@@ -4443,7 +4443,7 @@
     </row>
     <row r="9" spans="1:32">
       <c r="B9" s="79" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C9" s="81">
         <v>0</v>
@@ -4524,7 +4524,7 @@
     </row>
     <row r="10" spans="1:32">
       <c r="B10" s="74" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C10" s="74">
         <v>20</v>
@@ -4608,7 +4608,7 @@
     </row>
     <row r="11" spans="1:32">
       <c r="B11" s="74" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C11" s="81" t="str">
         <f>C8*C10</f>
@@ -4717,7 +4717,7 @@
     </row>
     <row r="12" spans="1:32">
       <c r="B12" s="79" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="81" t="str">
         <f>C10*C9</f>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="13" spans="1:32">
       <c r="B13" s="74" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C13" s="84" t="str">
         <f>C11/AB11</f>
@@ -4932,7 +4932,7 @@
     </row>
     <row r="14" spans="1:32">
       <c r="B14" s="74" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C14" s="81" t="str">
         <f>ROUNDUP(AB14*C13,2)</f>
@@ -5041,7 +5041,7 @@
     </row>
     <row r="15" spans="1:32">
       <c r="B15" s="74" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C15" s="81" t="str">
         <f>ROUNDUP(C11+C14,2)</f>
@@ -5150,7 +5150,7 @@
     </row>
     <row r="16" spans="1:32">
       <c r="B16" s="79" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C16" s="81" t="str">
         <f>ROUNDUP(C12+C14,2)</f>
@@ -5259,7 +5259,7 @@
     </row>
     <row r="17" spans="1:32">
       <c r="B17" s="74" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C17" s="81" t="str">
         <f>IF(AB15&gt;5000,ROUND(100*C13,2),ROUND(50*C13,2))</f>
@@ -5368,7 +5368,7 @@
     </row>
     <row r="18" spans="1:32">
       <c r="B18" s="74" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C18" s="81" t="str">
         <f>ROUNDUP(C15+C17,2)</f>
@@ -5477,7 +5477,7 @@
     </row>
     <row r="19" spans="1:32">
       <c r="B19" s="79" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C19" s="81" t="str">
         <f>ROUNDUP(C16+C17,2)</f>
@@ -5586,7 +5586,7 @@
     </row>
     <row r="23" spans="1:32">
       <c r="B23" s="75" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C23" s="74"/>
       <c r="D23" s="74"/>
@@ -5594,7 +5594,7 @@
     </row>
     <row r="26" spans="1:32">
       <c r="B26" s="74" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C26" s="81">
         <v>0</v>
@@ -5759,7 +5759,7 @@
     </row>
     <row r="28" spans="1:32">
       <c r="B28" s="74" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C28" s="81" t="str">
         <f>MAX(C19,C18)*C27</f>
@@ -5868,7 +5868,7 @@
     </row>
     <row r="29" spans="1:32">
       <c r="B29" s="74" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C29" s="81" t="str">
         <f>0.16*(MAX(C19,C18)+C28)</f>
@@ -5977,7 +5977,7 @@
     </row>
     <row r="30" spans="1:32">
       <c r="B30" s="74" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C30" s="81" t="str">
         <f>0.02*(MAX(C19,C18)+C28)</f>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="31" spans="1:32">
       <c r="B31" s="74" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C31" s="81" t="str">
         <f>0.035*(MAX(C18,C19) +C28+C29+C30)</f>
@@ -6195,7 +6195,7 @@
     </row>
     <row r="32" spans="1:32">
       <c r="B32" s="74" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C32" s="81" t="str">
         <f>SUM(C28:C31)</f>
@@ -6304,7 +6304,7 @@
     </row>
     <row r="37" spans="1:32">
       <c r="B37" s="75" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C37" s="74"/>
       <c r="D37" s="74"/>
@@ -6312,7 +6312,7 @@
     </row>
     <row r="40" spans="1:32">
       <c r="B40" s="74" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C40" s="81" t="str">
         <f>C13*AB40</f>
@@ -6424,90 +6424,90 @@
     </row>
     <row r="43" spans="1:32">
       <c r="B43" s="74" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C43" s="74" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D43" s="74" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E43" s="74" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F43" s="74" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G43" s="74" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H43" s="74" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I43" s="74" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J43" s="74" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K43" s="74" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L43" s="74" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M43" s="74" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N43" s="74" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O43" s="74" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P43" s="74" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q43" s="74" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R43" s="74" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S43" s="74" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T43" s="74" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="U43" s="74" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V43" s="74" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="W43" s="74" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="X43" s="74" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Y43" s="74" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z43" s="74" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AA43" s="74" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AB43" s="74" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:32">
       <c r="B44" s="74" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C44" s="81" t="str">
         <f>SUM(C15,C40,C32,(C26*C10))</f>
@@ -6616,7 +6616,7 @@
     </row>
     <row r="45" spans="1:32">
       <c r="B45" s="74" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C45" s="74">
         <v>20</v>
@@ -6697,7 +6697,7 @@
     </row>
     <row r="46" spans="1:32">
       <c r="B46" s="74" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C46" s="81" t="str">
         <f>ROUND(SUM(C44/C45),2)</f>
@@ -6803,7 +6803,7 @@
     </row>
     <row r="47" spans="1:32">
       <c r="B47" s="74" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C47" s="85" t="str">
         <f>ROUND(C46*3.7,2)</f>

--- a/assets/downloads/CotizacionEdwing Saavedra Valeriano.xlsx
+++ b/assets/downloads/CotizacionEdwing Saavedra Valeriano.xlsx
@@ -53,7 +53,7 @@
     <t>PESO:</t>
   </si>
   <si>
-    <t>0 Kg</t>
+    <t>91 Kg</t>
   </si>
   <si>
     <t>DNI/RUC:</t>
@@ -71,10 +71,13 @@
     <t>TELEFONO:</t>
   </si>
   <si>
+    <t>915 125 848</t>
+  </si>
+  <si>
     <t>CLIENTE:</t>
   </si>
   <si>
-    <t>No existe en contenedor</t>
+    <t>NUEVO</t>
   </si>
   <si>
     <t>CBM</t>
@@ -113,9 +116,9 @@
     <t>Hola Edwing Saavedra Valeriano 😁 un gusto saludarte!
         A continuación te envío la cotización final de tu importación📋📦.
         🙋‍♂️ PAGO PENDIENTE :
-        ☑️Costo CBM: $0
-        ☑️Impuestos: $2959.53
-        ☑️ Total: $2959.53
+        ☑️Costo CBM: $1108.79604
+        ☑️Impuestos: $3083.49
+        ☑️ Total: $4192.28604
         Pronto le aviso nuevos avances, que tengan buen día🚢
         Último día de pago:</t>
   </si>
@@ -489,9 +492,6 @@
   </si>
   <si>
     <t>Valor CBM</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>Valor Unitario</t>
@@ -1764,7 +1764,9 @@
       <c r="B10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="16"/>
+      <c r="C10" s="16">
+        <v>25866466</v>
+      </c>
       <c r="D10" s="34"/>
       <c r="E10" s="27" t="s">
         <v>13</v>
@@ -1785,18 +1787,20 @@
       <c r="B11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="17"/>
+      <c r="C11" s="17" t="s">
+        <v>17</v>
+      </c>
       <c r="D11" s="35"/>
       <c r="E11" s="24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" s="48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G11" s="65"/>
       <c r="H11" s="33"/>
       <c r="I11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J11" s="95" t="str">
         <f>'2'!AB7</f>
@@ -1820,7 +1824,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="B13" s="66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" s="66"/>
       <c r="D13" s="66"/>
@@ -1831,15 +1835,15 @@
       <c r="I13" s="66"/>
       <c r="J13" s="66"/>
       <c r="K13" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="B14" s="67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" s="67"/>
       <c r="D14" s="67"/>
@@ -1854,12 +1858,12 @@
         <v>0</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="B15" s="68" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" s="68"/>
       <c r="D15" s="68"/>
@@ -1874,12 +1878,12 @@
         <v>0</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="B16" s="51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" s="51"/>
       <c r="D16" s="51"/>
@@ -1894,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1925,7 +1929,7 @@
     </row>
     <row r="19" spans="1:14">
       <c r="B19" s="69" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19" s="69"/>
       <c r="D19" s="69"/>
@@ -1935,18 +1939,18 @@
       <c r="H19" s="18"/>
       <c r="I19" s="18"/>
       <c r="J19" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="B20" s="49" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C20" s="49"/>
       <c r="D20" s="49"/>
@@ -1964,15 +1968,15 @@
         <v>0</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="B21" s="49" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C21" s="49"/>
       <c r="D21" s="49"/>
@@ -1989,12 +1993,12 @@
         <v>0</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="B22" s="48" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C22" s="48"/>
       <c r="D22" s="48"/>
@@ -2011,12 +2015,12 @@
         <v>0</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="B23" s="51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C23" s="51"/>
       <c r="D23" s="51"/>
@@ -2031,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -2049,7 +2053,7 @@
     </row>
     <row r="25" spans="1:14">
       <c r="B25" s="48" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C25" s="48"/>
       <c r="D25" s="48"/>
@@ -2059,19 +2063,19 @@
       <c r="H25" s="48"/>
       <c r="I25" s="48"/>
       <c r="J25" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K25" s="15" t="str">
         <f>'2'!AB31</f>
         <v>0</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="B26" s="51" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C26" s="51"/>
       <c r="D26" s="51"/>
@@ -2085,7 +2089,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -2100,7 +2104,7 @@
     </row>
     <row r="28" spans="1:14" customHeight="1" ht="15.6">
       <c r="B28" s="52" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C28" s="52"/>
       <c r="D28" s="52"/>
@@ -2111,15 +2115,15 @@
       <c r="I28" s="52"/>
       <c r="J28" s="52"/>
       <c r="K28" s="28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L28" s="28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="B29" s="49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C29" s="49"/>
       <c r="D29" s="49"/>
@@ -2134,12 +2138,12 @@
         <v>0</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="B30" s="49" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C30" s="49"/>
       <c r="D30" s="49"/>
@@ -2154,12 +2158,12 @@
         <v>0</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="B31" s="48" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C31" s="48"/>
       <c r="D31" s="48"/>
@@ -2174,12 +2178,12 @@
         <v>0</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="B32" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C32" s="51"/>
       <c r="D32" s="51"/>
@@ -2194,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -2212,7 +2216,7 @@
     </row>
     <row r="34" spans="1:14">
       <c r="B34" s="59" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C34" s="60"/>
       <c r="D34" s="60"/>
@@ -2227,28 +2231,28 @@
     </row>
     <row r="35" spans="1:14">
       <c r="B35" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C35" s="56" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D35" s="57"/>
       <c r="E35" s="58"/>
       <c r="F35" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G35" s="56" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H35" s="58"/>
       <c r="I35" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J35" s="26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K35" s="47" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L35" s="47"/>
     </row>
@@ -2257,7 +2261,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
@@ -2290,7 +2294,7 @@
         <v>2</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
@@ -2323,7 +2327,7 @@
         <v>3</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
@@ -2356,7 +2360,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
@@ -2389,7 +2393,7 @@
         <v>5</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -2421,7 +2425,7 @@
         <v>6</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
@@ -2453,7 +2457,7 @@
         <v>7</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
@@ -2485,7 +2489,7 @@
         <v>8</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
@@ -2517,7 +2521,7 @@
         <v>9</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
@@ -2549,7 +2553,7 @@
         <v>10</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
@@ -2581,7 +2585,7 @@
         <v>11</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
@@ -2613,7 +2617,7 @@
         <v>12</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
@@ -2645,7 +2649,7 @@
         <v>13</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
@@ -2677,7 +2681,7 @@
         <v>14</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
@@ -2709,7 +2713,7 @@
         <v>15</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
@@ -2741,7 +2745,7 @@
         <v>16</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
@@ -2773,7 +2777,7 @@
         <v>17</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
@@ -2805,7 +2809,7 @@
         <v>18</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
@@ -2837,7 +2841,7 @@
         <v>19</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
@@ -2869,7 +2873,7 @@
         <v>20</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
@@ -2901,7 +2905,7 @@
         <v>21</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
@@ -2933,7 +2937,7 @@
         <v>22</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
@@ -2965,7 +2969,7 @@
         <v>23</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
@@ -2997,7 +3001,7 @@
         <v>24</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
@@ -3029,7 +3033,7 @@
         <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
@@ -3058,7 +3062,7 @@
     </row>
     <row r="61" spans="1:14" customHeight="1" ht="18">
       <c r="B61" s="93" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C61" s="92"/>
       <c r="D61" s="92"/>
@@ -3183,7 +3187,7 @@
     </row>
     <row r="64" spans="1:14" customHeight="1" ht="18">
       <c r="B64" s="64" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C64" s="64"/>
       <c r="D64" s="64"/>
@@ -3282,7 +3286,7 @@
       <c r="B69" s="38"/>
       <c r="C69" s="38"/>
       <c r="D69" s="53" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E69" s="53"/>
       <c r="F69" s="53"/>
@@ -3300,7 +3304,7 @@
     </row>
     <row r="72" spans="1:14" customHeight="1" ht="21">
       <c r="B72" s="70" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C72" s="70"/>
       <c r="D72" s="70"/>
@@ -3315,7 +3319,7 @@
     </row>
     <row r="74" spans="1:14">
       <c r="B74" s="71" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C74" s="71"/>
       <c r="D74" s="71"/>
@@ -3330,7 +3334,7 @@
     </row>
     <row r="75" spans="1:14">
       <c r="B75" s="71" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C75" s="71"/>
       <c r="D75" s="71"/>
@@ -3345,7 +3349,7 @@
     </row>
     <row r="76" spans="1:14">
       <c r="B76" s="49" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C76" s="49"/>
       <c r="D76" s="49"/>
@@ -3360,7 +3364,7 @@
     </row>
     <row r="77" spans="1:14">
       <c r="B77" s="71" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C77" s="71"/>
       <c r="D77" s="71"/>
@@ -3375,7 +3379,7 @@
     </row>
     <row r="78" spans="1:14">
       <c r="B78" s="71" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C78" s="71"/>
       <c r="D78" s="71"/>
@@ -3390,7 +3394,7 @@
     </row>
     <row r="79" spans="1:14">
       <c r="B79" s="49" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C79" s="49"/>
       <c r="D79" s="49"/>
@@ -3405,7 +3409,7 @@
     </row>
     <row r="80" spans="1:14">
       <c r="B80" s="71" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C80" s="71"/>
       <c r="D80" s="71"/>
@@ -3420,7 +3424,7 @@
     </row>
     <row r="81" spans="1:14">
       <c r="B81" s="71" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C81" s="71"/>
       <c r="D81" s="71"/>
@@ -3435,7 +3439,7 @@
     </row>
     <row r="82" spans="1:14">
       <c r="B82" s="71" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C82" s="71"/>
       <c r="D82" s="71"/>
@@ -3450,7 +3454,7 @@
     </row>
     <row r="83" spans="1:14">
       <c r="B83" s="71" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C83" s="71"/>
       <c r="D83" s="71"/>
@@ -3465,7 +3469,7 @@
     </row>
     <row r="84" spans="1:14">
       <c r="B84" s="71" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C84" s="71"/>
       <c r="D84" s="71"/>
@@ -3480,7 +3484,7 @@
     </row>
     <row r="85" spans="1:14">
       <c r="B85" s="71" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C85" s="71"/>
       <c r="D85" s="71"/>
@@ -3495,7 +3499,7 @@
     </row>
     <row r="86" spans="1:14">
       <c r="B86" s="71" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C86" s="71"/>
       <c r="D86" s="71"/>
@@ -3510,7 +3514,7 @@
     </row>
     <row r="87" spans="1:14">
       <c r="B87" s="71" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C87" s="71"/>
       <c r="D87" s="71"/>
@@ -3525,7 +3529,7 @@
     </row>
     <row r="88" spans="1:14">
       <c r="B88" s="71" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C88" s="71"/>
       <c r="D88" s="71"/>
@@ -3540,7 +3544,7 @@
     </row>
     <row r="89" spans="1:14">
       <c r="B89" s="71" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C89" s="71"/>
       <c r="D89" s="71"/>
@@ -3598,7 +3602,7 @@
     </row>
     <row r="91" spans="1:14">
       <c r="B91" s="67" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C91" s="67"/>
       <c r="D91" s="67"/>
@@ -3613,7 +3617,7 @@
     </row>
     <row r="92" spans="1:14">
       <c r="B92" s="71" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C92" s="71"/>
       <c r="D92" s="71"/>
@@ -3628,7 +3632,7 @@
     </row>
     <row r="93" spans="1:14">
       <c r="B93" s="67" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C93" s="67"/>
       <c r="D93" s="67"/>
@@ -3643,7 +3647,7 @@
     </row>
     <row r="94" spans="1:14">
       <c r="B94" s="71" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C94" s="71"/>
       <c r="D94" s="71"/>
@@ -3658,7 +3662,7 @@
     </row>
     <row r="95" spans="1:14">
       <c r="B95" s="71" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C95" s="71"/>
       <c r="D95" s="71"/>
@@ -3673,7 +3677,7 @@
     </row>
     <row r="96" spans="1:14">
       <c r="B96" s="71" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C96" s="71"/>
       <c r="D96" s="71"/>
@@ -3688,7 +3692,7 @@
     </row>
     <row r="97" spans="1:14">
       <c r="B97" s="71" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C97" s="71"/>
       <c r="D97" s="71"/>
@@ -3703,7 +3707,7 @@
     </row>
     <row r="98" spans="1:14">
       <c r="B98" s="71" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C98" s="71"/>
       <c r="D98" s="71"/>
@@ -3719,7 +3723,7 @@
     <row r="99" spans="1:14">
       <c r="A99" s="32"/>
       <c r="B99" s="72" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C99" s="72"/>
       <c r="D99" s="72"/>
@@ -3735,7 +3739,7 @@
     <row r="100" spans="1:14">
       <c r="A100" s="32"/>
       <c r="B100" s="71" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C100" s="71"/>
       <c r="D100" s="71"/>
@@ -3751,7 +3755,7 @@
     <row r="101" spans="1:14">
       <c r="A101" s="32"/>
       <c r="B101" s="72" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C101" s="72"/>
       <c r="D101" s="72"/>
@@ -4089,7 +4093,7 @@
   <sheetData>
     <row r="3" spans="1:32">
       <c r="B3" s="75" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C3" s="74"/>
       <c r="D3" s="74"/>
@@ -4099,90 +4103,90 @@
     </row>
     <row r="5" spans="1:32">
       <c r="B5" s="78" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C5" s="80" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" s="80" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" s="80" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F5" s="80" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G5" s="80" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H5" s="80" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I5" s="80" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J5" s="80" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K5" s="80" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L5" s="80" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M5" s="80" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N5" s="80" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O5" s="80" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P5" s="80" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q5" s="80" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R5" s="80" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S5" s="80" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T5" s="80" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="U5" s="80" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V5" s="80" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="W5" s="80" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="X5" s="80" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Y5" s="80" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z5" s="80" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AA5" s="80" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AB5" s="80" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:32">
       <c r="B6" s="74" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" s="74">
         <v>0</v>
@@ -4260,18 +4264,18 @@
         <v>0</v>
       </c>
       <c r="AB6" s="82">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AE6" s="76" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AF6" s="76" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:32">
       <c r="B7" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C7" s="74">
         <v>0</v>
@@ -4348,13 +4352,15 @@
       <c r="AA7" s="74">
         <v>0</v>
       </c>
-      <c r="AB7" s="83" t="s">
-        <v>115</v>
+      <c r="AB7" s="83">
+        <v>0.3</v>
       </c>
       <c r="AE7" s="77" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF7" s="77"/>
+        <v>19</v>
+      </c>
+      <c r="AF7" s="77">
+        <v>933.33</v>
+      </c>
     </row>
     <row r="8" spans="1:32">
       <c r="B8" s="74" t="s">
@@ -5864,7 +5870,7 @@
     </row>
     <row r="29" spans="1:32">
       <c r="B29" s="74" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C29" s="81" t="str">
         <f>0.16*(MAX(C19,C18)+C28)</f>
@@ -5973,7 +5979,7 @@
     </row>
     <row r="30" spans="1:32">
       <c r="B30" s="74" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C30" s="81" t="str">
         <f>0.02*(MAX(C19,C18)+C28)</f>
@@ -6191,7 +6197,7 @@
     </row>
     <row r="32" spans="1:32">
       <c r="B32" s="74" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C32" s="81" t="str">
         <f>SUM(C28:C31)</f>
@@ -6423,82 +6429,82 @@
         <v>133</v>
       </c>
       <c r="C43" s="74" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D43" s="74" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E43" s="74" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F43" s="74" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G43" s="74" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H43" s="74" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I43" s="74" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J43" s="74" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K43" s="74" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L43" s="74" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M43" s="74" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N43" s="74" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O43" s="74" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P43" s="74" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q43" s="74" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R43" s="74" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S43" s="74" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T43" s="74" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="U43" s="74" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V43" s="74" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="W43" s="74" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="X43" s="74" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Y43" s="74" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z43" s="74" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AA43" s="74" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AB43" s="74" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:32">
@@ -6612,7 +6618,7 @@
     </row>
     <row r="45" spans="1:32">
       <c r="B45" s="74" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C45" s="74">
         <v>20</v>

--- a/assets/downloads/CotizacionEdwing Saavedra Valeriano.xlsx
+++ b/assets/downloads/CotizacionEdwing Saavedra Valeriano.xlsx
@@ -71,7 +71,7 @@
     <t>TELEFONO:</t>
   </si>
   <si>
-    <t>915 125 848</t>
+    <t>51 934 958 839</t>
   </si>
   <si>
     <t>CLIENTE:</t>
@@ -117,8 +117,8 @@
         A continuación te envío la cotización final de tu importación📋📦.
         🙋‍♂️ PAGO PENDIENTE :
         ☑️Costo CBM: $1108.79604
-        ☑️Impuestos: $3083.49
-        ☑️ Total: $4192.28604
+        ☑️Impuestos: $3455.23
+        ☑️ Total: $4564.02604
         Pronto le aviso nuevos avances, que tengan buen día🚢
         Último día de pago:</t>
   </si>
@@ -4353,7 +4353,7 @@
         <v>0</v>
       </c>
       <c r="AB7" s="83">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="AE7" s="77" t="s">
         <v>19</v>
@@ -4937,107 +4937,107 @@
         <v>122</v>
       </c>
       <c r="C14" s="81" t="str">
-        <f>ROUNDUP(AB14*C13,2)</f>
+        <f>AB14*C13</f>
         <v>0</v>
       </c>
       <c r="D14" s="81" t="str">
-        <f>ROUNDUP(AB14*D13,2)</f>
+        <f>AB14*D13</f>
         <v>0</v>
       </c>
       <c r="E14" s="81" t="str">
-        <f>ROUNDUP(AB14*E13,2)</f>
+        <f>AB14*E13</f>
         <v>0</v>
       </c>
       <c r="F14" s="81" t="str">
-        <f>ROUNDUP(AB14*F13,2)</f>
+        <f>AB14*F13</f>
         <v>0</v>
       </c>
       <c r="G14" s="81" t="str">
-        <f>ROUNDUP(AB14*G13,2)</f>
+        <f>AB14*G13</f>
         <v>0</v>
       </c>
       <c r="H14" s="81" t="str">
-        <f>ROUNDUP(AB14*H13,2)</f>
+        <f>AB14*H13</f>
         <v>0</v>
       </c>
       <c r="I14" s="81" t="str">
-        <f>ROUNDUP(AB14*I13,2)</f>
+        <f>AB14*I13</f>
         <v>0</v>
       </c>
       <c r="J14" s="81" t="str">
-        <f>ROUNDUP(AB14*J13,2)</f>
+        <f>AB14*J13</f>
         <v>0</v>
       </c>
       <c r="K14" s="81" t="str">
-        <f>ROUNDUP(AB14*K13,2)</f>
+        <f>AB14*K13</f>
         <v>0</v>
       </c>
       <c r="L14" s="81" t="str">
-        <f>ROUNDUP(AB14*L13,2)</f>
+        <f>AB14*L13</f>
         <v>0</v>
       </c>
       <c r="M14" s="81" t="str">
-        <f>ROUNDUP(AB14*M13,2)</f>
+        <f>AB14*M13</f>
         <v>0</v>
       </c>
       <c r="N14" s="81" t="str">
-        <f>ROUNDUP(AB14*N13,2)</f>
+        <f>AB14*N13</f>
         <v>0</v>
       </c>
       <c r="O14" s="81" t="str">
-        <f>ROUNDUP(AB14*O13,2)</f>
+        <f>AB14*O13</f>
         <v>0</v>
       </c>
       <c r="P14" s="81" t="str">
-        <f>ROUNDUP(AB14*P13,2)</f>
+        <f>AB14*P13</f>
         <v>0</v>
       </c>
       <c r="Q14" s="81" t="str">
-        <f>ROUNDUP(AB14*Q13,2)</f>
+        <f>AB14*Q13</f>
         <v>0</v>
       </c>
       <c r="R14" s="81" t="str">
-        <f>ROUNDUP(AB14*R13,2)</f>
+        <f>AB14*R13</f>
         <v>0</v>
       </c>
       <c r="S14" s="81" t="str">
-        <f>ROUNDUP(AB14*S13,2)</f>
+        <f>AB14*S13</f>
         <v>0</v>
       </c>
       <c r="T14" s="81" t="str">
-        <f>ROUNDUP(AB14*T13,2)</f>
+        <f>AB14*T13</f>
         <v>0</v>
       </c>
       <c r="U14" s="81" t="str">
-        <f>ROUNDUP(AB14*U13,2)</f>
+        <f>AB14*U13</f>
         <v>0</v>
       </c>
       <c r="V14" s="81" t="str">
-        <f>ROUNDUP(AB14*V13,2)</f>
+        <f>AB14*V13</f>
         <v>0</v>
       </c>
       <c r="W14" s="81" t="str">
-        <f>ROUNDUP(AB14*W13,2)</f>
+        <f>AB14*W13</f>
         <v>0</v>
       </c>
       <c r="X14" s="81" t="str">
-        <f>ROUNDUP(AB14*X13,2)</f>
+        <f>AB14*X13</f>
         <v>0</v>
       </c>
       <c r="Y14" s="81" t="str">
-        <f>ROUNDUP(AB14*Y13,2)</f>
+        <f>AB14*Y13</f>
         <v>0</v>
       </c>
       <c r="Z14" s="81" t="str">
-        <f>ROUNDUP(AB14*Z13,2)</f>
+        <f>AB14*Z13</f>
         <v>0</v>
       </c>
       <c r="AA14" s="81" t="str">
-        <f>ROUNDUP(AB14*AA13,2)</f>
+        <f>AB14*AA13</f>
         <v>0</v>
       </c>
       <c r="AB14" s="86" t="str">
-        <f>IF(AB7&lt;1, ROUNDUP(AF7*0.6, 0), ROUNDUP(AF7*0.6*AB7, 0))</f>
+        <f>IF(AB7&lt;1, AF7*0.6, AF7*0.6*AB7)</f>
         <v>0</v>
       </c>
     </row>
@@ -5046,103 +5046,103 @@
         <v>123</v>
       </c>
       <c r="C15" s="81" t="str">
-        <f>ROUNDUP(C11+C14,2)</f>
+        <f>C11+C14</f>
         <v>0</v>
       </c>
       <c r="D15" s="81" t="str">
-        <f>ROUNDUP(D11+D14,2)</f>
+        <f>D11+D14</f>
         <v>0</v>
       </c>
       <c r="E15" s="81" t="str">
-        <f>ROUNDUP(E11+E14,2)</f>
+        <f>E11+E14</f>
         <v>0</v>
       </c>
       <c r="F15" s="81" t="str">
-        <f>ROUNDUP(F11+F14,2)</f>
+        <f>F11+F14</f>
         <v>0</v>
       </c>
       <c r="G15" s="81" t="str">
-        <f>ROUNDUP(G11+G14,2)</f>
+        <f>G11+G14</f>
         <v>0</v>
       </c>
       <c r="H15" s="81" t="str">
-        <f>ROUNDUP(H11+H14,2)</f>
+        <f>H11+H14</f>
         <v>0</v>
       </c>
       <c r="I15" s="81" t="str">
-        <f>ROUNDUP(I11+I14,2)</f>
+        <f>I11+I14</f>
         <v>0</v>
       </c>
       <c r="J15" s="81" t="str">
-        <f>ROUNDUP(J11+J14,2)</f>
+        <f>J11+J14</f>
         <v>0</v>
       </c>
       <c r="K15" s="81" t="str">
-        <f>ROUNDUP(K11+K14,2)</f>
+        <f>K11+K14</f>
         <v>0</v>
       </c>
       <c r="L15" s="81" t="str">
-        <f>ROUNDUP(L11+L14,2)</f>
+        <f>L11+L14</f>
         <v>0</v>
       </c>
       <c r="M15" s="81" t="str">
-        <f>ROUNDUP(M11+M14,2)</f>
+        <f>M11+M14</f>
         <v>0</v>
       </c>
       <c r="N15" s="81" t="str">
-        <f>ROUNDUP(N11+N14,2)</f>
+        <f>N11+N14</f>
         <v>0</v>
       </c>
       <c r="O15" s="81" t="str">
-        <f>ROUNDUP(O11+O14,2)</f>
+        <f>O11+O14</f>
         <v>0</v>
       </c>
       <c r="P15" s="81" t="str">
-        <f>ROUNDUP(P11+P14,2)</f>
+        <f>P11+P14</f>
         <v>0</v>
       </c>
       <c r="Q15" s="81" t="str">
-        <f>ROUNDUP(Q11+Q14,2)</f>
+        <f>Q11+Q14</f>
         <v>0</v>
       </c>
       <c r="R15" s="81" t="str">
-        <f>ROUNDUP(R11+R14,2)</f>
+        <f>R11+R14</f>
         <v>0</v>
       </c>
       <c r="S15" s="81" t="str">
-        <f>ROUNDUP(S11+S14,2)</f>
+        <f>S11+S14</f>
         <v>0</v>
       </c>
       <c r="T15" s="81" t="str">
-        <f>ROUNDUP(T11+T14,2)</f>
+        <f>T11+T14</f>
         <v>0</v>
       </c>
       <c r="U15" s="81" t="str">
-        <f>ROUNDUP(U11+U14,2)</f>
+        <f>U11+U14</f>
         <v>0</v>
       </c>
       <c r="V15" s="81" t="str">
-        <f>ROUNDUP(V11+V14,2)</f>
+        <f>V11+V14</f>
         <v>0</v>
       </c>
       <c r="W15" s="81" t="str">
-        <f>ROUNDUP(W11+W14,2)</f>
+        <f>W11+W14</f>
         <v>0</v>
       </c>
       <c r="X15" s="81" t="str">
-        <f>ROUNDUP(X11+X14,2)</f>
+        <f>X11+X14</f>
         <v>0</v>
       </c>
       <c r="Y15" s="81" t="str">
-        <f>ROUNDUP(Y11+Y14,2)</f>
+        <f>Y11+Y14</f>
         <v>0</v>
       </c>
       <c r="Z15" s="81" t="str">
-        <f>ROUNDUP(Z11+Z14,2)</f>
+        <f>Z11+Z14</f>
         <v>0</v>
       </c>
       <c r="AA15" s="81" t="str">
-        <f>ROUNDUP(AA11+AA14,2)</f>
+        <f>AA11+AA14</f>
         <v>0</v>
       </c>
       <c r="AB15" s="86" t="str">
@@ -5155,103 +5155,103 @@
         <v>124</v>
       </c>
       <c r="C16" s="81" t="str">
-        <f>ROUNDUP(C12+C14,2)</f>
+        <f>C12+C14</f>
         <v>0</v>
       </c>
       <c r="D16" s="81" t="str">
-        <f>ROUNDUP(D12+D14,2)</f>
+        <f>D12+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="81" t="str">
-        <f>ROUNDUP(E12+E14,2)</f>
+        <f>E12+E14</f>
         <v>0</v>
       </c>
       <c r="F16" s="81" t="str">
-        <f>ROUNDUP(F12+F14,2)</f>
+        <f>F12+F14</f>
         <v>0</v>
       </c>
       <c r="G16" s="81" t="str">
-        <f>ROUNDUP(G12+G14,2)</f>
+        <f>G12+G14</f>
         <v>0</v>
       </c>
       <c r="H16" s="81" t="str">
-        <f>ROUNDUP(H12+H14,2)</f>
+        <f>H12+H14</f>
         <v>0</v>
       </c>
       <c r="I16" s="81" t="str">
-        <f>ROUNDUP(I12+I14,2)</f>
+        <f>I12+I14</f>
         <v>0</v>
       </c>
       <c r="J16" s="81" t="str">
-        <f>ROUNDUP(J12+J14,2)</f>
+        <f>J12+J14</f>
         <v>0</v>
       </c>
       <c r="K16" s="81" t="str">
-        <f>ROUNDUP(K12+K14,2)</f>
+        <f>K12+K14</f>
         <v>0</v>
       </c>
       <c r="L16" s="81" t="str">
-        <f>ROUNDUP(L12+L14,2)</f>
+        <f>L12+L14</f>
         <v>0</v>
       </c>
       <c r="M16" s="81" t="str">
-        <f>ROUNDUP(M12+M14,2)</f>
+        <f>M12+M14</f>
         <v>0</v>
       </c>
       <c r="N16" s="81" t="str">
-        <f>ROUNDUP(N12+N14,2)</f>
+        <f>N12+N14</f>
         <v>0</v>
       </c>
       <c r="O16" s="81" t="str">
-        <f>ROUNDUP(O12+O14,2)</f>
+        <f>O12+O14</f>
         <v>0</v>
       </c>
       <c r="P16" s="81" t="str">
-        <f>ROUNDUP(P12+P14,2)</f>
+        <f>P12+P14</f>
         <v>0</v>
       </c>
       <c r="Q16" s="81" t="str">
-        <f>ROUNDUP(Q12+Q14,2)</f>
+        <f>Q12+Q14</f>
         <v>0</v>
       </c>
       <c r="R16" s="81" t="str">
-        <f>ROUNDUP(R12+R14,2)</f>
+        <f>R12+R14</f>
         <v>0</v>
       </c>
       <c r="S16" s="81" t="str">
-        <f>ROUNDUP(S12+S14,2)</f>
+        <f>S12+S14</f>
         <v>0</v>
       </c>
       <c r="T16" s="81" t="str">
-        <f>ROUNDUP(T12+T14,2)</f>
+        <f>T12+T14</f>
         <v>0</v>
       </c>
       <c r="U16" s="81" t="str">
-        <f>ROUNDUP(U12+U14,2)</f>
+        <f>U12+U14</f>
         <v>0</v>
       </c>
       <c r="V16" s="81" t="str">
-        <f>ROUNDUP(V12+V14,2)</f>
+        <f>V12+V14</f>
         <v>0</v>
       </c>
       <c r="W16" s="81" t="str">
-        <f>ROUNDUP(W12+W14,2)</f>
+        <f>W12+W14</f>
         <v>0</v>
       </c>
       <c r="X16" s="81" t="str">
-        <f>ROUNDUP(X12+X14,2)</f>
+        <f>X12+X14</f>
         <v>0</v>
       </c>
       <c r="Y16" s="81" t="str">
-        <f>ROUNDUP(Y12+Y14,2)</f>
+        <f>Y12+Y14</f>
         <v>0</v>
       </c>
       <c r="Z16" s="81" t="str">
-        <f>ROUNDUP(Z12+Z14,2)</f>
+        <f>Z12+Z14</f>
         <v>0</v>
       </c>
       <c r="AA16" s="81" t="str">
-        <f>ROUNDUP(AA12+AA14,2)</f>
+        <f>AA12+AA14</f>
         <v>0</v>
       </c>
       <c r="AB16" s="86" t="str">
@@ -5264,103 +5264,103 @@
         <v>125</v>
       </c>
       <c r="C17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*C13,2),ROUND(50*C13,2))</f>
+        <f>IF(AB15&gt;5000,100*C13,50*C13)</f>
         <v>0</v>
       </c>
       <c r="D17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*D13,2),ROUND(50*D13,2))</f>
+        <f>IF(AB15&gt;5000,100*D13,50*D13)</f>
         <v>0</v>
       </c>
       <c r="E17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*E13,2),ROUND(50*E13,2))</f>
+        <f>IF(AB15&gt;5000,100*E13,50*E13)</f>
         <v>0</v>
       </c>
       <c r="F17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*F13,2),ROUND(50*F13,2))</f>
+        <f>IF(AB15&gt;5000,100*F13,50*F13)</f>
         <v>0</v>
       </c>
       <c r="G17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*G13,2),ROUND(50*G13,2))</f>
+        <f>IF(AB15&gt;5000,100*G13,50*G13)</f>
         <v>0</v>
       </c>
       <c r="H17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*H13,2),ROUND(50*H13,2))</f>
+        <f>IF(AB15&gt;5000,100*H13,50*H13)</f>
         <v>0</v>
       </c>
       <c r="I17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*I13,2),ROUND(50*I13,2))</f>
+        <f>IF(AB15&gt;5000,100*I13,50*I13)</f>
         <v>0</v>
       </c>
       <c r="J17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*J13,2),ROUND(50*J13,2))</f>
+        <f>IF(AB15&gt;5000,100*J13,50*J13)</f>
         <v>0</v>
       </c>
       <c r="K17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*K13,2),ROUND(50*K13,2))</f>
+        <f>IF(AB15&gt;5000,100*K13,50*K13)</f>
         <v>0</v>
       </c>
       <c r="L17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*L13,2),ROUND(50*L13,2))</f>
+        <f>IF(AB15&gt;5000,100*L13,50*L13)</f>
         <v>0</v>
       </c>
       <c r="M17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*M13,2),ROUND(50*M13,2))</f>
+        <f>IF(AB15&gt;5000,100*M13,50*M13)</f>
         <v>0</v>
       </c>
       <c r="N17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*N13,2),ROUND(50*N13,2))</f>
+        <f>IF(AB15&gt;5000,100*N13,50*N13)</f>
         <v>0</v>
       </c>
       <c r="O17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*O13,2),ROUND(50*O13,2))</f>
+        <f>IF(AB15&gt;5000,100*O13,50*O13)</f>
         <v>0</v>
       </c>
       <c r="P17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*P13,2),ROUND(50*P13,2))</f>
+        <f>IF(AB15&gt;5000,100*P13,50*P13)</f>
         <v>0</v>
       </c>
       <c r="Q17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*Q13,2),ROUND(50*Q13,2))</f>
+        <f>IF(AB15&gt;5000,100*Q13,50*Q13)</f>
         <v>0</v>
       </c>
       <c r="R17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*R13,2),ROUND(50*R13,2))</f>
+        <f>IF(AB15&gt;5000,100*R13,50*R13)</f>
         <v>0</v>
       </c>
       <c r="S17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*S13,2),ROUND(50*S13,2))</f>
+        <f>IF(AB15&gt;5000,100*S13,50*S13)</f>
         <v>0</v>
       </c>
       <c r="T17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*T13,2),ROUND(50*T13,2))</f>
+        <f>IF(AB15&gt;5000,100*T13,50*T13)</f>
         <v>0</v>
       </c>
       <c r="U17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*U13,2),ROUND(50*U13,2))</f>
+        <f>IF(AB15&gt;5000,100*U13,50*U13)</f>
         <v>0</v>
       </c>
       <c r="V17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*V13,2),ROUND(50*V13,2))</f>
+        <f>IF(AB15&gt;5000,100*V13,50*V13)</f>
         <v>0</v>
       </c>
       <c r="W17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*W13,2),ROUND(50*W13,2))</f>
+        <f>IF(AB15&gt;5000,100*W13,50*W13)</f>
         <v>0</v>
       </c>
       <c r="X17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*X13,2),ROUND(50*X13,2))</f>
+        <f>IF(AB15&gt;5000,100*X13,50*X13)</f>
         <v>0</v>
       </c>
       <c r="Y17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*Y13,2),ROUND(50*Y13,2))</f>
+        <f>IF(AB15&gt;5000,100*Y13,50*Y13)</f>
         <v>0</v>
       </c>
       <c r="Z17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*Z13,2),ROUND(50*Z13,2))</f>
+        <f>IF(AB15&gt;5000,100*Z13,50*Z13)</f>
         <v>0</v>
       </c>
       <c r="AA17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*AA13,2),ROUND(50*AA13,2))</f>
+        <f>IF(AB15&gt;5000,100*AA13,50*AA13)</f>
         <v>0</v>
       </c>
       <c r="AB17" s="86" t="str">
@@ -5373,103 +5373,103 @@
         <v>126</v>
       </c>
       <c r="C18" s="81" t="str">
-        <f>ROUNDUP(C15+C17,2)</f>
+        <f>C15+C17</f>
         <v>0</v>
       </c>
       <c r="D18" s="81" t="str">
-        <f>ROUNDUP(D15+D17,2)</f>
+        <f>D15+D17</f>
         <v>0</v>
       </c>
       <c r="E18" s="81" t="str">
-        <f>ROUNDUP(E15+E17,2)</f>
+        <f>E15+E17</f>
         <v>0</v>
       </c>
       <c r="F18" s="81" t="str">
-        <f>ROUNDUP(F15+F17,2)</f>
+        <f>F15+F17</f>
         <v>0</v>
       </c>
       <c r="G18" s="81" t="str">
-        <f>ROUNDUP(G15+G17,2)</f>
+        <f>G15+G17</f>
         <v>0</v>
       </c>
       <c r="H18" s="81" t="str">
-        <f>ROUNDUP(H15+H17,2)</f>
+        <f>H15+H17</f>
         <v>0</v>
       </c>
       <c r="I18" s="81" t="str">
-        <f>ROUNDUP(I15+I17,2)</f>
+        <f>I15+I17</f>
         <v>0</v>
       </c>
       <c r="J18" s="81" t="str">
-        <f>ROUNDUP(J15+J17,2)</f>
+        <f>J15+J17</f>
         <v>0</v>
       </c>
       <c r="K18" s="81" t="str">
-        <f>ROUNDUP(K15+K17,2)</f>
+        <f>K15+K17</f>
         <v>0</v>
       </c>
       <c r="L18" s="81" t="str">
-        <f>ROUNDUP(L15+L17,2)</f>
+        <f>L15+L17</f>
         <v>0</v>
       </c>
       <c r="M18" s="81" t="str">
-        <f>ROUNDUP(M15+M17,2)</f>
+        <f>M15+M17</f>
         <v>0</v>
       </c>
       <c r="N18" s="81" t="str">
-        <f>ROUNDUP(N15+N17,2)</f>
+        <f>N15+N17</f>
         <v>0</v>
       </c>
       <c r="O18" s="81" t="str">
-        <f>ROUNDUP(O15+O17,2)</f>
+        <f>O15+O17</f>
         <v>0</v>
       </c>
       <c r="P18" s="81" t="str">
-        <f>ROUNDUP(P15+P17,2)</f>
+        <f>P15+P17</f>
         <v>0</v>
       </c>
       <c r="Q18" s="81" t="str">
-        <f>ROUNDUP(Q15+Q17,2)</f>
+        <f>Q15+Q17</f>
         <v>0</v>
       </c>
       <c r="R18" s="81" t="str">
-        <f>ROUNDUP(R15+R17,2)</f>
+        <f>R15+R17</f>
         <v>0</v>
       </c>
       <c r="S18" s="81" t="str">
-        <f>ROUNDUP(S15+S17,2)</f>
+        <f>S15+S17</f>
         <v>0</v>
       </c>
       <c r="T18" s="81" t="str">
-        <f>ROUNDUP(T15+T17,2)</f>
+        <f>T15+T17</f>
         <v>0</v>
       </c>
       <c r="U18" s="81" t="str">
-        <f>ROUNDUP(U15+U17,2)</f>
+        <f>U15+U17</f>
         <v>0</v>
       </c>
       <c r="V18" s="81" t="str">
-        <f>ROUNDUP(V15+V17,2)</f>
+        <f>V15+V17</f>
         <v>0</v>
       </c>
       <c r="W18" s="81" t="str">
-        <f>ROUNDUP(W15+W17,2)</f>
+        <f>W15+W17</f>
         <v>0</v>
       </c>
       <c r="X18" s="81" t="str">
-        <f>ROUNDUP(X15+X17,2)</f>
+        <f>X15+X17</f>
         <v>0</v>
       </c>
       <c r="Y18" s="81" t="str">
-        <f>ROUNDUP(Y15+Y17,2)</f>
+        <f>Y15+Y17</f>
         <v>0</v>
       </c>
       <c r="Z18" s="81" t="str">
-        <f>ROUNDUP(Z15+Z17,2)</f>
+        <f>Z15+Z17</f>
         <v>0</v>
       </c>
       <c r="AA18" s="81" t="str">
-        <f>ROUNDUP(AA15+AA17,2)</f>
+        <f>AA15+AA17</f>
         <v>0</v>
       </c>
       <c r="AB18" s="86" t="str">
@@ -5482,103 +5482,103 @@
         <v>127</v>
       </c>
       <c r="C19" s="81" t="str">
-        <f>ROUNDUP(C16+C17,2)</f>
+        <f>C16+C17</f>
         <v>0</v>
       </c>
       <c r="D19" s="81" t="str">
-        <f>ROUNDUP(D16+D17,2)</f>
+        <f>D16+D17</f>
         <v>0</v>
       </c>
       <c r="E19" s="81" t="str">
-        <f>ROUNDUP(E16+E17,2)</f>
+        <f>E16+E17</f>
         <v>0</v>
       </c>
       <c r="F19" s="81" t="str">
-        <f>ROUNDUP(F16+F17,2)</f>
+        <f>F16+F17</f>
         <v>0</v>
       </c>
       <c r="G19" s="81" t="str">
-        <f>ROUNDUP(G16+G17,2)</f>
+        <f>G16+G17</f>
         <v>0</v>
       </c>
       <c r="H19" s="81" t="str">
-        <f>ROUNDUP(H16+H17,2)</f>
+        <f>H16+H17</f>
         <v>0</v>
       </c>
       <c r="I19" s="81" t="str">
-        <f>ROUNDUP(I16+I17,2)</f>
+        <f>I16+I17</f>
         <v>0</v>
       </c>
       <c r="J19" s="81" t="str">
-        <f>ROUNDUP(J16+J17,2)</f>
+        <f>J16+J17</f>
         <v>0</v>
       </c>
       <c r="K19" s="81" t="str">
-        <f>ROUNDUP(K16+K17,2)</f>
+        <f>K16+K17</f>
         <v>0</v>
       </c>
       <c r="L19" s="81" t="str">
-        <f>ROUNDUP(L16+L17,2)</f>
+        <f>L16+L17</f>
         <v>0</v>
       </c>
       <c r="M19" s="81" t="str">
-        <f>ROUNDUP(M16+M17,2)</f>
+        <f>M16+M17</f>
         <v>0</v>
       </c>
       <c r="N19" s="81" t="str">
-        <f>ROUNDUP(N16+N17,2)</f>
+        <f>N16+N17</f>
         <v>0</v>
       </c>
       <c r="O19" s="81" t="str">
-        <f>ROUNDUP(O16+O17,2)</f>
+        <f>O16+O17</f>
         <v>0</v>
       </c>
       <c r="P19" s="81" t="str">
-        <f>ROUNDUP(P16+P17,2)</f>
+        <f>P16+P17</f>
         <v>0</v>
       </c>
       <c r="Q19" s="81" t="str">
-        <f>ROUNDUP(Q16+Q17,2)</f>
+        <f>Q16+Q17</f>
         <v>0</v>
       </c>
       <c r="R19" s="81" t="str">
-        <f>ROUNDUP(R16+R17,2)</f>
+        <f>R16+R17</f>
         <v>0</v>
       </c>
       <c r="S19" s="81" t="str">
-        <f>ROUNDUP(S16+S17,2)</f>
+        <f>S16+S17</f>
         <v>0</v>
       </c>
       <c r="T19" s="81" t="str">
-        <f>ROUNDUP(T16+T17,2)</f>
+        <f>T16+T17</f>
         <v>0</v>
       </c>
       <c r="U19" s="81" t="str">
-        <f>ROUNDUP(U16+U17,2)</f>
+        <f>U16+U17</f>
         <v>0</v>
       </c>
       <c r="V19" s="81" t="str">
-        <f>ROUNDUP(V16+V17,2)</f>
+        <f>V16+V17</f>
         <v>0</v>
       </c>
       <c r="W19" s="81" t="str">
-        <f>ROUNDUP(W16+W17,2)</f>
+        <f>W16+W17</f>
         <v>0</v>
       </c>
       <c r="X19" s="81" t="str">
-        <f>ROUNDUP(X16+X17,2)</f>
+        <f>X16+X17</f>
         <v>0</v>
       </c>
       <c r="Y19" s="81" t="str">
-        <f>ROUNDUP(Y16+Y17,2)</f>
+        <f>Y16+Y17</f>
         <v>0</v>
       </c>
       <c r="Z19" s="81" t="str">
-        <f>ROUNDUP(Z16+Z17,2)</f>
+        <f>Z16+Z17</f>
         <v>0</v>
       </c>
       <c r="AA19" s="81" t="str">
-        <f>ROUNDUP(AA16+AA17,2)</f>
+        <f>AA16+AA17</f>
         <v>0</v>
       </c>
       <c r="AB19" s="86" t="str">
@@ -6417,7 +6417,7 @@
         <v>0</v>
       </c>
       <c r="AB40" s="81" t="str">
-        <f>IF(AB7&lt;1, ROUNDUP(AF7*0.4, 0), ROUNDUP(AF7*0.4*AB7, 0))</f>
+        <f>IF(AB7&lt;1, AF7*0.4,AF7*0.4*AB7)</f>
         <v>0</v>
       </c>
     </row>
@@ -6512,103 +6512,103 @@
         <v>134</v>
       </c>
       <c r="C44" s="81" t="str">
-        <f>SUM(C15,C40,C32,(C26*C10))</f>
+        <f>SUM(C15,C40,C32,(C26))</f>
         <v>0</v>
       </c>
       <c r="D44" s="81" t="str">
-        <f>SUM(D15,D40,D32,(D26*D10))</f>
+        <f>SUM(D15,D40,D32,(D26))</f>
         <v>0</v>
       </c>
       <c r="E44" s="81" t="str">
-        <f>SUM(E15,E40,E32,(E26*E10))</f>
+        <f>SUM(E15,E40,E32,(E26))</f>
         <v>0</v>
       </c>
       <c r="F44" s="81" t="str">
-        <f>SUM(F15,F40,F32,(F26*F10))</f>
+        <f>SUM(F15,F40,F32,(F26))</f>
         <v>0</v>
       </c>
       <c r="G44" s="81" t="str">
-        <f>SUM(G15,G40,G32,(G26*G10))</f>
+        <f>SUM(G15,G40,G32,(G26))</f>
         <v>0</v>
       </c>
       <c r="H44" s="81" t="str">
-        <f>SUM(H15,H40,H32,(H26*H10))</f>
+        <f>SUM(H15,H40,H32,(H26))</f>
         <v>0</v>
       </c>
       <c r="I44" s="81" t="str">
-        <f>SUM(I15,I40,I32,(I26*I10))</f>
+        <f>SUM(I15,I40,I32,(I26))</f>
         <v>0</v>
       </c>
       <c r="J44" s="81" t="str">
-        <f>SUM(J15,J40,J32,(J26*J10))</f>
+        <f>SUM(J15,J40,J32,(J26))</f>
         <v>0</v>
       </c>
       <c r="K44" s="81" t="str">
-        <f>SUM(K15,K40,K32,(K26*K10))</f>
+        <f>SUM(K15,K40,K32,(K26))</f>
         <v>0</v>
       </c>
       <c r="L44" s="81" t="str">
-        <f>SUM(L15,L40,L32,(L26*L10))</f>
+        <f>SUM(L15,L40,L32,(L26))</f>
         <v>0</v>
       </c>
       <c r="M44" s="81" t="str">
-        <f>SUM(M15,M40,M32,(M26*M10))</f>
+        <f>SUM(M15,M40,M32,(M26))</f>
         <v>0</v>
       </c>
       <c r="N44" s="81" t="str">
-        <f>SUM(N15,N40,N32,(N26*N10))</f>
+        <f>SUM(N15,N40,N32,(N26))</f>
         <v>0</v>
       </c>
       <c r="O44" s="81" t="str">
-        <f>SUM(O15,O40,O32,(O26*O10))</f>
+        <f>SUM(O15,O40,O32,(O26))</f>
         <v>0</v>
       </c>
       <c r="P44" s="81" t="str">
-        <f>SUM(P15,P40,P32,(P26*P10))</f>
+        <f>SUM(P15,P40,P32,(P26))</f>
         <v>0</v>
       </c>
       <c r="Q44" s="81" t="str">
-        <f>SUM(Q15,Q40,Q32,(Q26*Q10))</f>
+        <f>SUM(Q15,Q40,Q32,(Q26))</f>
         <v>0</v>
       </c>
       <c r="R44" s="81" t="str">
-        <f>SUM(R15,R40,R32,(R26*R10))</f>
+        <f>SUM(R15,R40,R32,(R26))</f>
         <v>0</v>
       </c>
       <c r="S44" s="81" t="str">
-        <f>SUM(S15,S40,S32,(S26*S10))</f>
+        <f>SUM(S15,S40,S32,(S26))</f>
         <v>0</v>
       </c>
       <c r="T44" s="81" t="str">
-        <f>SUM(T15,T40,T32,(T26*T10))</f>
+        <f>SUM(T15,T40,T32,(T26))</f>
         <v>0</v>
       </c>
       <c r="U44" s="81" t="str">
-        <f>SUM(U15,U40,U32,(U26*U10))</f>
+        <f>SUM(U15,U40,U32,(U26))</f>
         <v>0</v>
       </c>
       <c r="V44" s="81" t="str">
-        <f>SUM(V15,V40,V32,(V26*V10))</f>
+        <f>SUM(V15,V40,V32,(V26))</f>
         <v>0</v>
       </c>
       <c r="W44" s="81" t="str">
-        <f>SUM(W15,W40,W32,(W26*W10))</f>
+        <f>SUM(W15,W40,W32,(W26))</f>
         <v>0</v>
       </c>
       <c r="X44" s="81" t="str">
-        <f>SUM(X15,X40,X32,(X26*X10))</f>
+        <f>SUM(X15,X40,X32,(X26))</f>
         <v>0</v>
       </c>
       <c r="Y44" s="81" t="str">
-        <f>SUM(Y15,Y40,Y32,(Y26*Y10))</f>
+        <f>SUM(Y15,Y40,Y32,(Y26))</f>
         <v>0</v>
       </c>
       <c r="Z44" s="81" t="str">
-        <f>SUM(Z15,Z40,Z32,(Z26*Z10))</f>
+        <f>SUM(Z15,Z40,Z32,(Z26))</f>
         <v>0</v>
       </c>
       <c r="AA44" s="81" t="str">
-        <f>SUM(AA15,AA40,AA32,(AA26*AA10))</f>
+        <f>SUM(AA15,AA40,AA32,(AA26))</f>
         <v>0</v>
       </c>
       <c r="AB44" s="81" t="str">
@@ -6702,103 +6702,103 @@
         <v>135</v>
       </c>
       <c r="C46" s="81" t="str">
-        <f>ROUND(SUM(C44/C45),2)</f>
+        <f>SUM(C44/C45)</f>
         <v>0</v>
       </c>
       <c r="D46" s="81" t="str">
-        <f>ROUND(SUM(D44/D45),2)</f>
+        <f>SUM(D44/D45)</f>
         <v>0</v>
       </c>
       <c r="E46" s="81" t="str">
-        <f>ROUND(SUM(E44/E45),2)</f>
+        <f>SUM(E44/E45)</f>
         <v>0</v>
       </c>
       <c r="F46" s="81" t="str">
-        <f>ROUND(SUM(F44/F45),2)</f>
+        <f>SUM(F44/F45)</f>
         <v>0</v>
       </c>
       <c r="G46" s="81" t="str">
-        <f>ROUND(SUM(G44/G45),2)</f>
+        <f>SUM(G44/G45)</f>
         <v>0</v>
       </c>
       <c r="H46" s="81" t="str">
-        <f>ROUND(SUM(H44/H45),2)</f>
+        <f>SUM(H44/H45)</f>
         <v>0</v>
       </c>
       <c r="I46" s="81" t="str">
-        <f>ROUND(SUM(I44/I45),2)</f>
+        <f>SUM(I44/I45)</f>
         <v>0</v>
       </c>
       <c r="J46" s="81" t="str">
-        <f>ROUND(SUM(J44/J45),2)</f>
+        <f>SUM(J44/J45)</f>
         <v>0</v>
       </c>
       <c r="K46" s="81" t="str">
-        <f>ROUND(SUM(K44/K45),2)</f>
+        <f>SUM(K44/K45)</f>
         <v>0</v>
       </c>
       <c r="L46" s="81" t="str">
-        <f>ROUND(SUM(L44/L45),2)</f>
+        <f>SUM(L44/L45)</f>
         <v>0</v>
       </c>
       <c r="M46" s="81" t="str">
-        <f>ROUND(SUM(M44/M45),2)</f>
+        <f>SUM(M44/M45)</f>
         <v>0</v>
       </c>
       <c r="N46" s="81" t="str">
-        <f>ROUND(SUM(N44/N45),2)</f>
+        <f>SUM(N44/N45)</f>
         <v>0</v>
       </c>
       <c r="O46" s="81" t="str">
-        <f>ROUND(SUM(O44/O45),2)</f>
+        <f>SUM(O44/O45)</f>
         <v>0</v>
       </c>
       <c r="P46" s="81" t="str">
-        <f>ROUND(SUM(P44/P45),2)</f>
+        <f>SUM(P44/P45)</f>
         <v>0</v>
       </c>
       <c r="Q46" s="81" t="str">
-        <f>ROUND(SUM(Q44/Q45),2)</f>
+        <f>SUM(Q44/Q45)</f>
         <v>0</v>
       </c>
       <c r="R46" s="81" t="str">
-        <f>ROUND(SUM(R44/R45),2)</f>
+        <f>SUM(R44/R45)</f>
         <v>0</v>
       </c>
       <c r="S46" s="81" t="str">
-        <f>ROUND(SUM(S44/S45),2)</f>
+        <f>SUM(S44/S45)</f>
         <v>0</v>
       </c>
       <c r="T46" s="81" t="str">
-        <f>ROUND(SUM(T44/T45),2)</f>
+        <f>SUM(T44/T45)</f>
         <v>0</v>
       </c>
       <c r="U46" s="81" t="str">
-        <f>ROUND(SUM(U44/U45),2)</f>
+        <f>SUM(U44/U45)</f>
         <v>0</v>
       </c>
       <c r="V46" s="81" t="str">
-        <f>ROUND(SUM(V44/V45),2)</f>
+        <f>SUM(V44/V45)</f>
         <v>0</v>
       </c>
       <c r="W46" s="81" t="str">
-        <f>ROUND(SUM(W44/W45),2)</f>
+        <f>SUM(W44/W45)</f>
         <v>0</v>
       </c>
       <c r="X46" s="81" t="str">
-        <f>ROUND(SUM(X44/X45),2)</f>
+        <f>SUM(X44/X45)</f>
         <v>0</v>
       </c>
       <c r="Y46" s="81" t="str">
-        <f>ROUND(SUM(Y44/Y45),2)</f>
+        <f>SUM(Y44/Y45)</f>
         <v>0</v>
       </c>
       <c r="Z46" s="81" t="str">
-        <f>ROUND(SUM(Z44/Z45),2)</f>
+        <f>SUM(Z44/Z45)</f>
         <v>0</v>
       </c>
       <c r="AA46" s="81" t="str">
-        <f>ROUND(SUM(AA44/AA45),2)</f>
+        <f>SUM(AA44/AA45)</f>
         <v>0</v>
       </c>
       <c r="AB46" s="74"/>
@@ -6808,103 +6808,103 @@
         <v>136</v>
       </c>
       <c r="C47" s="85" t="str">
-        <f>ROUND(C46*3.7,2)</f>
+        <f>C46*3.7</f>
         <v>0</v>
       </c>
       <c r="D47" s="85" t="str">
-        <f>ROUND(D46*3.7,2)</f>
+        <f>D46*3.7</f>
         <v>0</v>
       </c>
       <c r="E47" s="85" t="str">
-        <f>ROUND(E46*3.7,2)</f>
+        <f>E46*3.7</f>
         <v>0</v>
       </c>
       <c r="F47" s="85" t="str">
-        <f>ROUND(F46*3.7,2)</f>
+        <f>F46*3.7</f>
         <v>0</v>
       </c>
       <c r="G47" s="85" t="str">
-        <f>ROUND(G46*3.7,2)</f>
+        <f>G46*3.7</f>
         <v>0</v>
       </c>
       <c r="H47" s="85" t="str">
-        <f>ROUND(H46*3.7,2)</f>
+        <f>H46*3.7</f>
         <v>0</v>
       </c>
       <c r="I47" s="85" t="str">
-        <f>ROUND(I46*3.7,2)</f>
+        <f>I46*3.7</f>
         <v>0</v>
       </c>
       <c r="J47" s="85" t="str">
-        <f>ROUND(J46*3.7,2)</f>
+        <f>J46*3.7</f>
         <v>0</v>
       </c>
       <c r="K47" s="85" t="str">
-        <f>ROUND(K46*3.7,2)</f>
+        <f>K46*3.7</f>
         <v>0</v>
       </c>
       <c r="L47" s="85" t="str">
-        <f>ROUND(L46*3.7,2)</f>
+        <f>L46*3.7</f>
         <v>0</v>
       </c>
       <c r="M47" s="85" t="str">
-        <f>ROUND(M46*3.7,2)</f>
+        <f>M46*3.7</f>
         <v>0</v>
       </c>
       <c r="N47" s="85" t="str">
-        <f>ROUND(N46*3.7,2)</f>
+        <f>N46*3.7</f>
         <v>0</v>
       </c>
       <c r="O47" s="85" t="str">
-        <f>ROUND(O46*3.7,2)</f>
+        <f>O46*3.7</f>
         <v>0</v>
       </c>
       <c r="P47" s="85" t="str">
-        <f>ROUND(P46*3.7,2)</f>
+        <f>P46*3.7</f>
         <v>0</v>
       </c>
       <c r="Q47" s="85" t="str">
-        <f>ROUND(Q46*3.7,2)</f>
+        <f>Q46*3.7</f>
         <v>0</v>
       </c>
       <c r="R47" s="85" t="str">
-        <f>ROUND(R46*3.7,2)</f>
+        <f>R46*3.7</f>
         <v>0</v>
       </c>
       <c r="S47" s="85" t="str">
-        <f>ROUND(S46*3.7,2)</f>
+        <f>S46*3.7</f>
         <v>0</v>
       </c>
       <c r="T47" s="85" t="str">
-        <f>ROUND(T46*3.7,2)</f>
+        <f>T46*3.7</f>
         <v>0</v>
       </c>
       <c r="U47" s="85" t="str">
-        <f>ROUND(U46*3.7,2)</f>
+        <f>U46*3.7</f>
         <v>0</v>
       </c>
       <c r="V47" s="85" t="str">
-        <f>ROUND(V46*3.7,2)</f>
+        <f>V46*3.7</f>
         <v>0</v>
       </c>
       <c r="W47" s="85" t="str">
-        <f>ROUND(W46*3.7,2)</f>
+        <f>W46*3.7</f>
         <v>0</v>
       </c>
       <c r="X47" s="85" t="str">
-        <f>ROUND(X46*3.7,2)</f>
+        <f>X46*3.7</f>
         <v>0</v>
       </c>
       <c r="Y47" s="85" t="str">
-        <f>ROUND(Y46*3.7,2)</f>
+        <f>Y46*3.7</f>
         <v>0</v>
       </c>
       <c r="Z47" s="85" t="str">
-        <f>ROUND(Z46*3.7,2)</f>
+        <f>Z46*3.7</f>
         <v>0</v>
       </c>
       <c r="AA47" s="85" t="str">
-        <f>ROUND(AA46*3.7,2)</f>
+        <f>AA46*3.7</f>
         <v>0</v>
       </c>
       <c r="AB47" s="74"/>
